--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1217,11 +1217,6 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11">
-        <row r="10">
-          <cell r="B10">
-            <v>45777</v>
-          </cell>
-        </row>
         <row r="12">
           <cell r="B12">
             <v>45808</v>
@@ -1355,7 +1350,21 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
@@ -1429,7 +1438,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
@@ -1604,7 +1622,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45838</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1621,7 +1639,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45869</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1638,7 +1656,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45900</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1651,13 +1669,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45930</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1672,7 +1690,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45961</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1692,7 +1710,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>45991</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1707,7 +1725,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46022</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1729,7 +1747,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46053</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1744,7 +1762,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1765,7 +1783,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1780,7 +1798,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46142</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1802,7 +1820,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1817,7 +1835,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13408,7 +13426,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45838</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13425,7 +13443,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45869</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13442,7 +13460,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45900</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13455,13 +13473,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45930</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13476,7 +13494,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45961</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13496,7 +13514,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>45991</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13511,7 +13529,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46022</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13533,7 +13551,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46053</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13548,7 +13566,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13569,7 +13587,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13584,7 +13602,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46142</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13606,7 +13624,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13621,7 +13639,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13972,7 +13990,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45838</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13989,7 +14007,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45869</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14006,7 +14024,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45900</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14019,13 +14037,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45930</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14040,7 +14058,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45961</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14060,7 +14078,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>45991</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14075,7 +14093,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46022</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14097,7 +14115,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46053</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14112,7 +14130,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14133,7 +14151,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14148,7 +14166,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46142</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14170,7 +14188,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14185,7 +14203,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14536,7 +14554,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45838</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14553,7 +14571,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45869</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14570,7 +14588,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45900</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14583,13 +14601,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45930</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14604,7 +14622,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45961</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14624,7 +14642,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>45991</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14639,7 +14657,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46022</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14661,7 +14679,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46053</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14676,7 +14694,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14697,7 +14715,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14712,7 +14730,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46142</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14734,7 +14752,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14749,7 +14767,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15100,7 +15118,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45838</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15117,7 +15135,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45869</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15134,7 +15152,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45900</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15147,13 +15165,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45930</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15168,7 +15186,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45961</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15188,7 +15206,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>45991</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15203,7 +15221,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46022</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15225,7 +15243,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46053</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15240,7 +15258,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15261,7 +15279,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15276,7 +15294,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46142</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15298,7 +15316,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15313,7 +15331,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15707,12 +15725,12 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84"/>
       <c r="B4" s="85" t="n">
-        <f aca="false">[1]Admin!$B$10</f>
-        <v>45777</v>
+        <f aca="false">[1]Admin!$B$12</f>
+        <v>45808</v>
       </c>
       <c r="C4" s="85" t="n">
         <f aca="false">B5</f>
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="D4" s="86" t="n">
         <f aca="false">S02Y1!$H$1</f>
@@ -15744,12 +15762,12 @@
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="84"/>
       <c r="B5" s="85" t="n">
-        <f aca="false">[1]Admin!$B$12</f>
-        <v>45808</v>
+        <f aca="false">[1]Admin!$B$14</f>
+        <v>45838</v>
       </c>
       <c r="C5" s="85" t="n">
         <f aca="false">B6</f>
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="D5" s="86" t="n">
         <f aca="false">S03Y1!$H$1</f>
@@ -15781,12 +15799,12 @@
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="84"/>
       <c r="B6" s="85" t="n">
-        <f aca="false">[1]Admin!$B$14</f>
-        <v>45838</v>
+        <f aca="false">[1]Admin!$B$16</f>
+        <v>45869</v>
       </c>
       <c r="C6" s="85" t="n">
         <f aca="false">B7</f>
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="D6" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -15830,12 +15848,12 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="84"/>
       <c r="B7" s="85" t="n">
-        <f aca="false">[1]Admin!$B$16</f>
-        <v>45869</v>
+        <f aca="false">[1]Admin!$B$18</f>
+        <v>45900</v>
       </c>
       <c r="C7" s="85" t="n">
         <f aca="false">B8</f>
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="D7" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -15879,15 +15897,15 @@
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="n">
-        <f aca="false">[1]Admin!$B$18</f>
-        <v>45900</v>
+        <f aca="false">[1]Admin!$B$20</f>
+        <v>45930</v>
       </c>
       <c r="C8" s="85" t="n">
         <f aca="false">B9</f>
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="D8" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="E8" s="87" t="n">
@@ -15895,7 +15913,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="87" t="n">
@@ -15903,7 +15921,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="I8" s="87" t="n">
@@ -15911,7 +15929,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="K8" s="87" t="n">
@@ -15920,7 +15938,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -15928,15 +15946,15 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="n">
-        <f aca="false">[1]Admin!$B$20</f>
-        <v>45930</v>
+        <f aca="false">[1]Admin!$B$22</f>
+        <v>45961</v>
       </c>
       <c r="C9" s="85" t="n">
         <f aca="false">B10</f>
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="D9" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="E9" s="87" t="n">
@@ -15944,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="G9" s="87" t="n">
@@ -15952,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="87" t="n">
@@ -15960,7 +15978,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="K9" s="87" t="n">
@@ -15977,15 +15995,15 @@
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="84"/>
       <c r="B10" s="85" t="n">
-        <f aca="false">[1]Admin!$B$22</f>
-        <v>45961</v>
+        <f aca="false">[1]Admin!$B$24</f>
+        <v>45991</v>
       </c>
       <c r="C10" s="85" t="n">
         <f aca="false">B11</f>
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="D10" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="E10" s="87" t="n">
@@ -15993,7 +16011,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="87" t="n">
@@ -16001,7 +16019,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="I10" s="87" t="n">
@@ -16009,7 +16027,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="K10" s="87" t="n">
@@ -16018,7 +16036,7 @@
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="90"/>
@@ -16026,15 +16044,15 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="84"/>
       <c r="B11" s="85" t="n">
-        <f aca="false">[1]Admin!$B$24</f>
-        <v>45991</v>
+        <f aca="false">[1]Admin!$B$26</f>
+        <v>46022</v>
       </c>
       <c r="C11" s="85" t="n">
         <f aca="false">B12</f>
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="D11" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="E11" s="87" t="n">
@@ -16042,7 +16060,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="G11" s="87" t="n">
@@ -16050,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="87" t="n">
@@ -16058,7 +16076,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="K11" s="87" t="n">
@@ -16067,7 +16085,7 @@
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="90"/>
@@ -16075,12 +16093,12 @@
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="84"/>
       <c r="B12" s="85" t="n">
-        <f aca="false">[1]Admin!$B$26</f>
-        <v>46022</v>
+        <f aca="false">[1]Admin!$B$28</f>
+        <v>46053</v>
       </c>
       <c r="C12" s="85" t="n">
         <f aca="false">B13</f>
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="D12" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -16124,12 +16142,12 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="84"/>
       <c r="B13" s="85" t="n">
-        <f aca="false">[1]Admin!$B$28</f>
-        <v>46053</v>
+        <f aca="false">[1]Admin!$B$30</f>
+        <v>46081</v>
       </c>
       <c r="C13" s="85" t="n">
         <f aca="false">B14</f>
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="D13" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -16165,7 +16183,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -16173,15 +16191,15 @@
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="84"/>
       <c r="B14" s="85" t="n">
-        <f aca="false">[1]Admin!$B$30</f>
-        <v>46081</v>
+        <f aca="false">[1]Admin!$B$32</f>
+        <v>46112</v>
       </c>
       <c r="C14" s="85" t="n">
         <f aca="false">B15</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="D14" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="E14" s="87" t="n">
@@ -16189,7 +16207,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="G14" s="87" t="n">
@@ -16197,7 +16215,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="I14" s="87" t="n">
@@ -16205,7 +16223,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="K14" s="87" t="n">
@@ -16214,7 +16232,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -16222,15 +16240,15 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="84"/>
       <c r="B15" s="85" t="n">
-        <f aca="false">[1]Admin!$B$32</f>
-        <v>46112</v>
+        <f aca="false">[1]Admin!$B$34</f>
+        <v>46142</v>
       </c>
       <c r="C15" s="85" t="n">
         <f aca="false">B16</f>
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D15" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="E15" s="87" t="n">
@@ -16238,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="G15" s="87" t="n">
@@ -16246,7 +16264,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="87" t="n">
@@ -16254,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="K15" s="87" t="n">
@@ -16271,15 +16289,15 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="84"/>
       <c r="B16" s="85" t="n">
-        <f aca="false">[1]Admin!$B$34</f>
-        <v>46142</v>
+        <f aca="false">[1]Admin!$B$36</f>
+        <v>46173</v>
       </c>
       <c r="C16" s="85" t="n">
         <f aca="false">B17</f>
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D16" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="E16" s="87" t="n">
@@ -16287,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="87" t="n">
@@ -16295,7 +16313,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="I16" s="87" t="n">
@@ -16303,7 +16321,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="K16" s="87" t="n">
@@ -16312,7 +16330,7 @@
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="90"/>
@@ -16320,15 +16338,15 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="84"/>
       <c r="B17" s="85" t="n">
-        <f aca="false">[1]Admin!$B$36</f>
-        <v>46173</v>
+        <f aca="false">[1]Admin!$B$38</f>
+        <v>46203</v>
       </c>
       <c r="C17" s="85" t="n">
         <f aca="false">B18</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
       <c r="D17" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="E17" s="87" t="n">
@@ -16336,7 +16354,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="G17" s="87" t="n">
@@ -16344,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Jun!$H$1</f>
         <v>0</v>
       </c>
       <c r="I17" s="87" t="n">
@@ -16352,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="K17" s="87" t="n">
@@ -16361,7 +16379,7 @@
       </c>
       <c r="L17" s="88"/>
       <c r="M17" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="90"/>
@@ -16369,8 +16387,8 @@
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="84"/>
       <c r="B18" s="85" t="n">
-        <f aca="false">[1]Admin!$B$38</f>
-        <v>46203</v>
+        <f aca="false">[1]Admin!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C18" s="85" t="n">
         <f aca="false">B19</f>
@@ -16410,7 +16428,7 @@
       </c>
       <c r="L18" s="88"/>
       <c r="M18" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N18" s="90"/>
@@ -16418,7 +16436,7 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="84"/>
       <c r="B19" s="85" t="n">
-        <f aca="false">[1]Admin!$B$40</f>
+        <f aca="false">[1]Admin!$B$42</f>
         <v>0</v>
       </c>
       <c r="C19" s="91" t="n">
@@ -16459,7 +16477,7 @@
       </c>
       <c r="L19" s="88"/>
       <c r="M19" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N19" s="90"/>
